--- a/光伏配储项目/电价数据/2026/洲边站.xlsx
+++ b/光伏配储项目/电价数据/2026/洲边站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51163</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7623799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57486</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52044</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51878</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13057</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10609</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12156</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11127</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13424</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05002</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11153</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16344</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16625</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.14607</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09154999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08672000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10323</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15332</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25771</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24496</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.13158</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14436</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21581</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6592100000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55975</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5818099999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.37399</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.62713</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.64316</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82802</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6425700000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6574500000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.80835</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.2058</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6925800000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6025700000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.84738</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.66052</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.67216</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6265700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48081</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42591</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71182</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77909</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79837</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.53638</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.85726</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51832</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50508</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48793</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46956</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.60048</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74524</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43639</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52506</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17656</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06742000000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77027</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.22187</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.80932</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5415800000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14041</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.52308</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.81543</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.01478</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.97048</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.65226</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7966599999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.03592</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.74398</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.67914</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6088899999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77616</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.58931</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06998</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47396</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66995</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33463</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51735</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5341900000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.48203</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51706</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49081</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43101</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16951</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.9608</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.69592</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57263</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6468700000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.74234</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57608</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50528</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53754</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49165</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45512</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46244</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44573</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34236</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46073</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.05608</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.92422</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.10558</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10385</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17697</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.23187</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07138</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12711</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.23602</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21863</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23785</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20245</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12319</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44192</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.66462</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47129</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43101</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29973</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25922</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03989</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04722999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03599</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04704999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04434</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04670000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04194</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21826</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04622</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05520000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04757</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00367</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15818</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05789</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46734</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35063</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67979</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04378</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00417</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04386</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04636</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04361</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04417</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04847</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20002</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26897</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33544</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31762</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17101</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14777</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22663</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15631</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50774</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62209</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92055</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9155800000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8661599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29848</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8912899999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19086</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8706499999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54088</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33464</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03556</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53452</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79408</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52951</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77611</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8771599999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87549</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49605</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40368</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21078</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87901</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55113</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62561</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53928</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58561</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956699999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60172</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66247</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47477</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8799</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63046</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87879</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86133</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8657999999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45154</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91804</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46351</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49893</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16646</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19305</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59487</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8899199999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3304</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13803</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69808</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78831</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57741</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.4999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49908</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49371</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.10482</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6284099999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.93602</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90203</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.14619</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6994600000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.76452</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.95116</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.08218</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5771900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7485499999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46378</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32342</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42123</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.07651</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16622</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.8466</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17801</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.1852</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.15616</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15078</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16044</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15098</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15931</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15912</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.21552</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16047</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16566</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.46554</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43817</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34836</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53637</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26584</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20295</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24292</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24161</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28517</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24301</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35977</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.46185</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.53788</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.69292</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.6384500000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70658</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28414</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3494</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65318</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77197</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34382</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.81102</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.73509</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7269</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.5321</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.7364400000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.7230800000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6059600000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5864199999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6708500000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8247100000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.97027</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47623</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35975</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5379299999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48511</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49369</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39818</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44724</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.53327</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.7241000000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65419</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.27567</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5101100000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69638</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7290599999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59205</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8325399999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77249</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67548</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4823</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46844</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5563400000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45378</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46161</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18017</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.41508</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.44661</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36469</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23081</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13921</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25339</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25082</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17165</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18363</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22943</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25013</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23296</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23629</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16259</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24705</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00116</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03107</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11356</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01929</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03886</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.008970000000000001</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03415</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02985</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04670000000000001</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02281</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04895</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19202</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00083</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04898</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04875</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03398</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04302</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18198</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19177</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23221</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25877</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5618099999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25172</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23914</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25648</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24634</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21049</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23905</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27455</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26115</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24133</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27307</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2171</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6264299999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60109</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64228</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5774199999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15534</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11772</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23485</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17636</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10451</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11469</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06543</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09726</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01209</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16766</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02786</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10599</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11628</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13595</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02327</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08798</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10155</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09984999999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.1405</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32296</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.57025</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.55664</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48084</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14269</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32834</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.63105</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.59266</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50989</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.44553</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46889</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48945</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.61372</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42158</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49626</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1934</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36773</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48168</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47114</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.5425399999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58374</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58736</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5103799999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55253</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47154</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51724</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42192</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87425</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58572</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58489</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37248</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25657</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17958</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07534</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.22615</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17515</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01174</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17175</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06551</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06078</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08731</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06275</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16132</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24844</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35892</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8647899999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26093</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11419</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.21575</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.6652899999999999</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00384</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04878</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02045</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02604</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.21808</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23779</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.12748</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.08875</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5822000000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35902</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61707</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22976</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14369</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20527</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22885</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23053</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11395</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04738000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04703</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04181</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07837000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06296</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09656999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16976</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19524</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12372</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05540999999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11709</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18439</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23549</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24248</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20271</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24329</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36557</v>
       </c>
     </row>
   </sheetData>
